--- a/distribucion/excel_analisis_datos/codigos/c10_proyecto/productos.xlsx
+++ b/distribucion/excel_analisis_datos/codigos/c10_proyecto/productos.xlsx
@@ -494,11 +494,11 @@
         <v>350</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>152</v>
+        <v>235</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Proveedor B</t>
+          <t>Proveedor C</t>
         </is>
       </c>
     </row>
@@ -520,11 +520,11 @@
         <v>850</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>594</v>
+        <v>436</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Proveedor C</t>
+          <t>Proveedor A</t>
         </is>
       </c>
     </row>
@@ -546,11 +546,11 @@
         <v>3200</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1566</v>
+        <v>2038</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Proveedor A</t>
+          <t>Proveedor C</t>
         </is>
       </c>
     </row>
@@ -572,11 +572,11 @@
         <v>1200</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>810</v>
+        <v>691</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Proveedor C</t>
+          <t>Proveedor A</t>
         </is>
       </c>
     </row>
@@ -598,11 +598,11 @@
         <v>250</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Proveedor A</t>
+          <t>Proveedor B</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
         <v>180</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -650,11 +650,11 @@
         <v>65</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Proveedor C</t>
+          <t>Proveedor A</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Proveedor B</t>
+          <t>Proveedor A</t>
         </is>
       </c>
     </row>
